--- a/out/thesis/tables/model_type_counts.xlsx
+++ b/out/thesis/tables/model_type_counts.xlsx
@@ -394,7 +394,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -416,7 +416,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -427,7 +427,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -438,7 +438,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -449,7 +449,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -460,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -482,7 +482,7 @@
         <v>8</v>
       </c>
       <c r="C10">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/out/thesis/tables/model_type_counts.xlsx
+++ b/out/thesis/tables/model_type_counts.xlsx
@@ -394,7 +394,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -416,7 +416,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -427,7 +427,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -435,10 +435,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -446,10 +446,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -460,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -468,10 +468,10 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -479,10 +479,10 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
